--- a/quizzes/005_seasons_and_axial_tilt_quiz--quizzes.xlsx
+++ b/quizzes/005_seasons_and_axial_tilt_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Summer'}</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Winter'}</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'autumn'}</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Autumn'}</t>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Spring'}</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'autumn'}</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Autumn'}</t>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_"the_tilt_is_in_sync_with_earth's_seasons."}</t>
+          <t>the_tilt_is_in_sync_with_earth's_seasons.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': "The tilt is in sync with Earth's seasons."}</t>
+          <t>The tilt is in sync with Earth's seasons.</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_"the_tilt_is_not_in_sync_with_earth's_seasons."}</t>
+          <t>the_tilt_is_not_in_sync_with_earth's_seasons.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': "The tilt is not in sync with Earth's seasons."}</t>
+          <t>The tilt is not in sync with Earth's seasons.</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_know."}</t>
+          <t>i_don't_know.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': "I don't know."}</t>
+          <t>I don't know.</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_"changes_in_earth's_temperature."}</t>
+          <t>changes_in_earth's_temperature.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': "Changes in Earth's temperature."}</t>
+          <t>Changes in Earth's temperature.</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_"changes_in_earth's_precipitation."}</t>
+          <t>changes_in_earth's_precipitation.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': "Changes in Earth's precipitation."}</t>
+          <t>Changes in Earth's precipitation.</t>
         </is>
       </c>
     </row>
@@ -915,12 +915,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_"changes_in_earth's_atmospheric_pressure."}</t>
+          <t>changes_in_earth's_atmospheric_pressure.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': "Changes in Earth's atmospheric pressure."}</t>
+          <t>Changes in Earth's atmospheric pressure.</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_know."}</t>
+          <t>i_don't_know.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': "I don't know."}</t>
+          <t>I don't know.</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_"to_understand_the_effects_of_the_tilt_on_earth's_climate."}</t>
+          <t>to_understand_the_effects_of_the_tilt_on_earth's_climate.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': "To understand the effects of the tilt on Earth's climate."}</t>
+          <t>To understand the effects of the tilt on Earth's climate.</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_"to_understand_the_effects_of_the_tilt_on_earth's_geography."}</t>
+          <t>to_understand_the_effects_of_the_tilt_on_earth's_geography.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': "To understand the effects of the tilt on Earth's geography."}</t>
+          <t>To understand the effects of the tilt on Earth's geography.</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_"to_understand_the_effects_of_the_tilt_on_earth's_oceans."}</t>
+          <t>to_understand_the_effects_of_the_tilt_on_earth's_oceans.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': "To understand the effects of the tilt on Earth's oceans."}</t>
+          <t>To understand the effects of the tilt on Earth's oceans.</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_"i_don't_know."}</t>
+          <t>i_don't_know.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': "I don't know."}</t>
+          <t>I don't know.</t>
         </is>
       </c>
     </row>
